--- a/error_models/conv_models/nv_8x8_b1_dat-524288_wt-32768_int8/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_8x8_b1_dat-524288_wt-32768_int8/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,13 +682,13 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9918707524405098</v>
+        <v>0.9935126358524562</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0081168789049</v>
+        <v>0.0064774405322694</v>
       </c>
       <c r="I2" t="n">
-        <v>1.229459817434395e-05</v>
+        <v>9.849558858795656e-06</v>
       </c>
       <c r="J2" t="n">
         <v>0.8348764953403011</v>
@@ -591,6 +721,84 @@
         <v>8.45399505050083e-07</v>
       </c>
       <c r="T2" t="n">
+        <v>0</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.0591694709353376</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.9408305290646624</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -616,19 +824,19 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9954255212872734</v>
+        <v>0.9957876585236424</v>
       </c>
       <c r="H3" t="n">
-        <v>0.004560863071486</v>
+        <v>0.0042010725225242</v>
       </c>
       <c r="I3" t="n">
-        <v>1.354158482496284e-05</v>
+        <v>1.119489741759265e-05</v>
       </c>
       <c r="J3" t="n">
         <v>0.6533730019874479</v>
       </c>
       <c r="K3" t="n">
-        <v>0.1867147477092028</v>
+        <v>0.1867147477092027</v>
       </c>
       <c r="L3" t="n">
         <v>0.1378884276974253</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>6.88903866022055e-05</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.0591692535935819</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.9408307464064182</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -680,19 +966,19 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9985521745496082</v>
+        <v>0.998627882358355</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0014338382902065</v>
+        <v>0.001360093224445</v>
       </c>
       <c r="I4" t="n">
-        <v>1.3913103769458e-05</v>
+        <v>1.195036078419393e-05</v>
       </c>
       <c r="J4" t="n">
         <v>0.1270936853959442</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7113480858124838</v>
+        <v>0.7113480858124837</v>
       </c>
       <c r="L4" t="n">
         <v>0.048088291903377</v>
@@ -701,7 +987,7 @@
         <v>0.0042377050200226</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0979749516449978</v>
+        <v>0.0979749516449977</v>
       </c>
       <c r="O4" t="n">
         <v>0.0095575413156486</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>0.0001127305799429</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9977560986321156</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.0022439013678844</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.0591698558388248</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.9408301441611751</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -744,13 +1108,13 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9970981657810412</v>
+        <v>0.997181177076602</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0028880539930927</v>
+        <v>0.0028069800279304</v>
       </c>
       <c r="I5" t="n">
-        <v>1.370616945046763e-05</v>
+        <v>1.176883905189352e-05</v>
       </c>
       <c r="J5" t="n">
         <v>0.2397922243700651</v>
@@ -774,7 +1138,7 @@
         <v>8.764989235048805e-07</v>
       </c>
       <c r="Q5" t="n">
-        <v>5.646874424495405e-06</v>
+        <v>5.646874424495404e-06</v>
       </c>
       <c r="R5" t="n">
         <v>0.0008553556769254</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0004682050663232</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0.997693537504767</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.002306462495233</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0.0591741576156335</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.9408258423843664</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -808,19 +1250,19 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9983003215631016</v>
+        <v>0.9983876091132184</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0016855843544763</v>
+        <v>0.0016002678487227</v>
       </c>
       <c r="I6" t="n">
-        <v>1.402002600625486e-05</v>
+        <v>1.204898164318243e-05</v>
       </c>
       <c r="J6" t="n">
         <v>0.1778168759913771</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6609050142338453</v>
+        <v>0.6609050142338452</v>
       </c>
       <c r="L6" t="n">
         <v>0.0497824335413831</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.0005124095302176</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0.997769684316312</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.002230315683688</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0.0591758843019952</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0.9408241156980048</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -872,13 +1392,13 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9910196255280816</v>
+        <v>0.9938117585028076</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0089668357903949</v>
+        <v>0.0061770389265429</v>
       </c>
       <c r="I7" t="n">
-        <v>1.346462510740275e-05</v>
+        <v>1.112851423369073e-05</v>
       </c>
       <c r="J7" t="n">
         <v>0.8348770273212863</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>0.003170631057407</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0.059169649138453</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.9408303508615468</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -936,16 +1534,16 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9957117009037488</v>
+        <v>0.9966561710628696</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0042748972180139</v>
+        <v>0.0033326563843456</v>
       </c>
       <c r="I8" t="n">
-        <v>1.332782182157343e-05</v>
+        <v>1.109849636893409e-05</v>
       </c>
       <c r="J8" t="n">
-        <v>0.804037633692904</v>
+        <v>0.8040376336929038</v>
       </c>
       <c r="K8" t="n">
         <v>0.0365691283605194</v>
@@ -972,10 +1570,88 @@
         <v>9.829428136086295e-07</v>
       </c>
       <c r="S8" t="n">
-        <v>3.310376749909379e-05</v>
+        <v>3.31037674990938e-05</v>
       </c>
       <c r="T8" t="n">
         <v>0.0015091202705345</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>0.0591694170261715</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.9408305829738286</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -1000,16 +1676,16 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.994818939913594</v>
+        <v>0.9974299600561068</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0051656250636719</v>
+        <v>0.0025562538250257</v>
       </c>
       <c r="I9" t="n">
-        <v>1.536096631841822e-05</v>
+        <v>1.371206245168927e-05</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8251655714516918</v>
+        <v>0.8251655714516919</v>
       </c>
       <c r="K9" t="n">
         <v>0.0175372451766649</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>1.023745739478731e-07</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1064,19 +1818,19 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9994744879972424</v>
+        <v>0.9995232528800918</v>
       </c>
       <c r="H10" t="n">
-        <v>0.000511456663121</v>
+        <v>0.0004641697450873</v>
       </c>
       <c r="I10" t="n">
-        <v>1.398128322090631e-05</v>
+        <v>1.250331840518282e-05</v>
       </c>
       <c r="J10" t="n">
         <v>0.0544590400976317</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7880475875508055</v>
+        <v>0.7880475875508054</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1103,6 +1857,84 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1128,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9998257084959048</v>
+        <v>0.9998541419167586</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0001598329054629</v>
+        <v>0.0001331275496864</v>
       </c>
       <c r="I11" t="n">
-        <v>1.438454221636902e-05</v>
+        <v>1.265647713927788e-05</v>
       </c>
       <c r="J11" t="n">
         <v>0.0002731173916353</v>
@@ -1167,6 +1999,84 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1192,16 +2102,16 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9977528110128032</v>
+        <v>0.9984813890240608</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0022322025949552</v>
+        <v>0.0015051246672201</v>
       </c>
       <c r="I12" t="n">
-        <v>1.491233582552763e-05</v>
+        <v>1.341225230335372e-05</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5459615353413961</v>
+        <v>0.545961535341396</v>
       </c>
       <c r="K12" t="n">
         <v>0</v>
@@ -1213,13 +2123,13 @@
         <v>0.0040917606973372</v>
       </c>
       <c r="N12" t="n">
-        <v>4.970715545886122e-06</v>
+        <v>4.970715545886123e-06</v>
       </c>
       <c r="O12" t="n">
         <v>8.621111920645587e-10</v>
       </c>
       <c r="P12" t="n">
-        <v>0.2889755567033943</v>
+        <v>0.2889755567033945</v>
       </c>
       <c r="Q12" t="n">
         <v>0.1553299528009764</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>4.989069498768733e-07</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1256,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9990550174383868</v>
+        <v>0.9995771474077644</v>
       </c>
       <c r="H13" t="n">
-        <v>0.0009298188716916</v>
+        <v>0.0004095366623882</v>
       </c>
       <c r="I13" t="n">
-        <v>1.508963350609853e-05</v>
+        <v>1.324187343157978e-05</v>
       </c>
       <c r="J13" t="n">
         <v>0.4585621839624038</v>
@@ -1296,6 +2284,84 @@
       </c>
       <c r="T13" t="n">
         <v>8.176820366136963e-09</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9971849805233516</v>
+        <v>0.9979201499628388</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0028000151572589</v>
+        <v>0.0020663091380945</v>
       </c>
       <c r="I14" t="n">
-        <v>1.493026297367065e-05</v>
+        <v>1.346684265080122e-05</v>
       </c>
       <c r="J14" t="n">
         <v>0.6268229243187448</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>0.0001967226067144</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9987076804466108</v>
+        <v>0.9994306098579584</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0012771597592242</v>
+        <v>0.0005560870569037</v>
       </c>
       <c r="I15" t="n">
-        <v>1.508573774905526e-05</v>
+        <v>1.322902872211719e-05</v>
       </c>
       <c r="J15" t="n">
         <v>0.682547168259441</v>
@@ -1405,7 +2549,7 @@
         <v>9.681630117391977e-07</v>
       </c>
       <c r="N15" t="n">
-        <v>6.401587345653963e-06</v>
+        <v>6.401587345653962e-06</v>
       </c>
       <c r="O15" t="n">
         <v>0</v>
@@ -1423,6 +2567,84 @@
         <v>0.008232872270393401</v>
       </c>
       <c r="T15" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1448,16 +2670,16 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9995171457332735</v>
+        <v>0.9997226840382528</v>
       </c>
       <c r="H16" t="n">
-        <v>0.000468262016224</v>
+        <v>0.0002647115581634</v>
       </c>
       <c r="I16" t="n">
-        <v>1.451819408656732e-05</v>
+        <v>1.253034716798421e-05</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1748085214302702</v>
+        <v>0.1748085214302703</v>
       </c>
       <c r="K16" t="n">
         <v>0.0012174359399308</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>3.160472688966129e-08</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9988770081415032</v>
+        <v>0.9990654127194044</v>
       </c>
       <c r="H17" t="n">
-        <v>0.001108420623604</v>
+        <v>0.0009214914810683</v>
       </c>
       <c r="I17" t="n">
-        <v>1.449717847704208e-05</v>
+        <v>1.302174311162207e-05</v>
       </c>
       <c r="J17" t="n">
         <v>0.2101986987663695</v>
@@ -1542,7 +2842,7 @@
         <v>0.6287073463827871</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.1518070187248879</v>
+        <v>0.1518070187248878</v>
       </c>
       <c r="R17" t="n">
         <v>0.0005308149295432</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0006042456352474</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1576,19 +2954,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9994888369925272</v>
+        <v>0.9997378424585046</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0004963022348801</v>
+        <v>0.00024927215548</v>
       </c>
       <c r="I18" t="n">
-        <v>1.478671617683773e-05</v>
+        <v>1.281132959945893e-05</v>
       </c>
       <c r="J18" t="n">
-        <v>0.3242934006503287</v>
+        <v>0.3242934006503286</v>
       </c>
       <c r="K18" t="n">
-        <v>4.109083627006374e-06</v>
+        <v>4.109083627006373e-06</v>
       </c>
       <c r="L18" t="n">
         <v>3.313497873057887e-08</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>5.522496455097102e-08</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1640,19 +3096,19 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9995936844794752</v>
+        <v>0.9996490877540858</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0003920084157376</v>
+        <v>0.0003381793562304</v>
       </c>
       <c r="I19" t="n">
-        <v>1.423304837142312e-05</v>
+        <v>1.265883326800121e-05</v>
       </c>
       <c r="J19" t="n">
         <v>0.0540303549031347</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8372260806889253</v>
+        <v>0.8372260806889252</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1679,6 +3135,84 @@
         <v>0</v>
       </c>
       <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1704,13 +3238,13 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.99968232517274</v>
+        <v>0.9997956779211638</v>
       </c>
       <c r="H20" t="n">
-        <v>0.000303012227236</v>
+        <v>0.0001915326010309</v>
       </c>
       <c r="I20" t="n">
-        <v>1.458854360800361e-05</v>
+        <v>1.271542138952982e-05</v>
       </c>
       <c r="J20" t="n">
         <v>0.1577470771767243</v>
@@ -1743,6 +3277,84 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1768,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9992091414525964</v>
+        <v>0.9992892497710084</v>
       </c>
       <c r="H21" t="n">
-        <v>0.0007762951188379</v>
+        <v>0.0006976641539212</v>
       </c>
       <c r="I21" t="n">
-        <v>1.448937215019112e-05</v>
+        <v>1.30120186546188e-05</v>
       </c>
       <c r="J21" t="n">
         <v>0.1141116026430236</v>
@@ -1807,6 +3419,84 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1832,37 +3522,37 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0926023453925874</v>
+        <v>0.6100778852204668</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9073833056764828</v>
+        <v>0.3899088624841677</v>
       </c>
       <c r="I22" t="n">
-        <v>1.427487451375533e-05</v>
+        <v>1.317823894983643e-05</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0011657143604619</v>
+        <v>0.0010598566252329</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9928601005804688</v>
+        <v>0.9931896769916282</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>6.460756007255454e-10</v>
+        <v>2.197029589491661e-07</v>
       </c>
       <c r="N22" t="n">
-        <v>2.374999305469752e-08</v>
+        <v>4.071739273694216e-07</v>
       </c>
       <c r="O22" t="n">
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.279564064555377e-08</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.0059740866065848</v>
+        <v>0.005749742654196</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -1871,6 +3561,84 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1896,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.8447459107901066</v>
+        <v>0.849619843055416</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1552390629268773</v>
+        <v>0.1503665030342704</v>
       </c>
       <c r="I23" t="n">
-        <v>1.495222660011897e-05</v>
+        <v>1.357985389770894e-05</v>
       </c>
       <c r="J23" t="n">
         <v>0.7490931311545371</v>
@@ -1936,6 +3704,84 @@
       </c>
       <c r="T23" t="n">
         <v>1.50751772998031e-07</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -1960,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.9959960731666954</v>
+        <v>0.9969203171364168</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0039889163777275</v>
+        <v>0.0030660794901345</v>
       </c>
       <c r="I24" t="n">
-        <v>1.493639916133291e-05</v>
+        <v>1.352931703307087e-05</v>
       </c>
       <c r="J24" t="n">
         <v>0.7319165460057344</v>
@@ -1990,7 +3836,7 @@
         <v>0.1030307140283908</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.1553196338975888</v>
+        <v>0.1553196338975889</v>
       </c>
       <c r="R24" t="n">
         <v>1.701916952541651e-06</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>3.824119192613262e-07</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>0</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9980633891927558</v>
+        <v>0.99822173033103</v>
       </c>
       <c r="H25" t="n">
-        <v>0.001922014586921</v>
+        <v>0.0017650888944236</v>
       </c>
       <c r="I25" t="n">
-        <v>1.452216390743271e-05</v>
+        <v>1.310671813053641e-05</v>
       </c>
       <c r="J25" t="n">
         <v>0.1886735821305832</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0005155839655283</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.998632973328356</v>
+        <v>0.9986642406912952</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0013530731290278</v>
+        <v>0.0013236604156025</v>
       </c>
       <c r="I26" t="n">
-        <v>1.387948620059983e-05</v>
+        <v>1.202483668635819e-05</v>
       </c>
       <c r="J26" t="n">
         <v>0.054155158835871</v>
@@ -2115,10 +4117,10 @@
         <v>0.0267776151395616</v>
       </c>
       <c r="P26" t="n">
-        <v>0.7824741558372608</v>
+        <v>0.7824741558372607</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.488971115664637e-06</v>
+        <v>5.488971115664638e-06</v>
       </c>
       <c r="R26" t="n">
         <v>0.0005399506622531</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0016207567775533</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0.9977146818047896</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0.0022853181952102</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0.0591701533909508</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0.9408298466090492</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2152,28 +4232,28 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9945981544267052</v>
+        <v>0.9954259104361576</v>
       </c>
       <c r="H27" t="n">
-        <v>0.005388153179715</v>
+        <v>0.004562655570326</v>
       </c>
       <c r="I27" t="n">
-        <v>1.3618337163821e-05</v>
+        <v>1.135993710049844e-05</v>
       </c>
       <c r="J27" t="n">
-        <v>0.7882756533315014</v>
+        <v>0.7882756533315015</v>
       </c>
       <c r="K27" t="n">
         <v>0.0524010163783766</v>
       </c>
       <c r="L27" t="n">
-        <v>0.1080435183069255</v>
+        <v>0.1080435183069254</v>
       </c>
       <c r="M27" t="n">
         <v>0.0039335998119396</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0337678154696598</v>
+        <v>0.0337678154696597</v>
       </c>
       <c r="O27" t="n">
         <v>0.0106112866643418</v>
@@ -2191,7 +4271,85 @@
         <v>2.411262824865157e-06</v>
       </c>
       <c r="T27" t="n">
-        <v>3.20044415828836e-05</v>
+        <v>3.200444158288361e-05</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0.9984650367362796</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0.0015349632637204</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0.0591694422784894</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0.9408305577215106</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9980000974758556</v>
+        <v>0.9982289232609139</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0019861563750428</v>
+        <v>0.0017594505921931</v>
       </c>
       <c r="I28" t="n">
-        <v>1.367209268591234e-05</v>
+        <v>1.155209047714058e-05</v>
       </c>
       <c r="J28" t="n">
         <v>0.3628753196206373</v>
@@ -2243,19 +4401,97 @@
         <v>0.016640519078381</v>
       </c>
       <c r="P28" t="n">
-        <v>0.4723445499442208</v>
+        <v>0.4723445499442209</v>
       </c>
       <c r="Q28" t="n">
         <v>9.283059906026031e-06</v>
       </c>
       <c r="R28" t="n">
-        <v>4.414732866450058e-05</v>
+        <v>4.414732866450059e-05</v>
       </c>
       <c r="S28" t="n">
         <v>0.0029745035709341</v>
       </c>
       <c r="T28" t="n">
         <v>0.000220715745511</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0.9977795906018876</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0.0022204093981123</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9952592312682006</v>
+        <v>0.9955043119590306</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0047270824225629</v>
+        <v>0.0044841352278984</v>
       </c>
       <c r="I29" t="n">
-        <v>1.361225282083423e-05</v>
+        <v>1.147875665545848e-05</v>
       </c>
       <c r="J29" t="n">
         <v>0.456245978587135</v>
@@ -2307,10 +4543,10 @@
         <v>0.0232074834731449</v>
       </c>
       <c r="P29" t="n">
-        <v>0.3791755542656135</v>
+        <v>0.3791755542656134</v>
       </c>
       <c r="Q29" t="n">
-        <v>7.269696105626182e-06</v>
+        <v>7.269696105626184e-06</v>
       </c>
       <c r="R29" t="n">
         <v>0.0012769352910598</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.0006794430305623</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0.9977687856899746</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0.0022312143100253</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0.0591808907862606</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0.9408191092137392</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2344,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.09312618278210109</v>
+        <v>0.6100708955441373</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9068600576248124</v>
+        <v>0.3899167062750741</v>
       </c>
       <c r="I30" t="n">
-        <v>1.368553667083373e-05</v>
+        <v>1.232412437279761e-05</v>
       </c>
       <c r="J30" t="n">
         <v>0.0015971629698457</v>
@@ -2383,6 +4697,84 @@
         <v>0</v>
       </c>
       <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2408,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9937573263316184</v>
+        <v>0.9954182950692519</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0062280861482888</v>
+        <v>0.0045685472938587</v>
       </c>
       <c r="I31" t="n">
-        <v>1.451346367695572e-05</v>
+        <v>1.308358047353169e-05</v>
       </c>
       <c r="J31" t="n">
         <v>0.2343492812055353</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>9.109269773091807e-07</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>0</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -2472,13 +4942,13 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.09716808450821419</v>
+        <v>0.6136184078730865</v>
       </c>
       <c r="H32" t="n">
-        <v>0.9028170242588448</v>
+        <v>0.3863680658256649</v>
       </c>
       <c r="I32" t="n">
-        <v>1.481717652506262e-05</v>
+        <v>1.345224483284425e-05</v>
       </c>
       <c r="J32" t="n">
         <v>0.0005839822143495</v>
@@ -2511,6 +4981,84 @@
         <v>1.308976227828103e-07</v>
       </c>
       <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>0</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2536,19 +5084,19 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.0973634236126683</v>
+        <v>0.4000551901277922</v>
       </c>
       <c r="H33" t="n">
-        <v>0.9026233302594738</v>
+        <v>0.5999340180037078</v>
       </c>
       <c r="I33" t="n">
-        <v>1.317207144202914e-05</v>
+        <v>1.071781208420934e-05</v>
       </c>
       <c r="J33" t="n">
         <v>0.0011647845300437</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9982856955606686</v>
+        <v>0.9982856955606684</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
@@ -2566,7 +5114,7 @@
         <v>7.561544785276933e-08</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.163671725390784e-07</v>
+        <v>5.163671725390783e-07</v>
       </c>
       <c r="R33" t="n">
         <v>6.565505764578927e-08</v>
@@ -2575,6 +5123,84 @@
         <v>0</v>
       </c>
       <c r="T33" t="n">
+        <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>0</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2600,13 +5226,13 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2021131421345547</v>
+        <v>0.458233490801388</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7978741659746167</v>
+        <v>0.5417562358642501</v>
       </c>
       <c r="I34" t="n">
-        <v>1.261783441277086e-05</v>
+        <v>1.019927794611022e-05</v>
       </c>
       <c r="J34" t="n">
         <v>0.0006782071499024</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>2.362977859917696e-07</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9874762306680356</v>
+        <v>0.991653459109336</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01251047355385545</v>
+        <v>0.008335592112708149</v>
       </c>
       <c r="I35" t="n">
-        <v>1.322172169320205e-05</v>
+        <v>1.087472153986128e-05</v>
       </c>
       <c r="J35" t="n">
         <v>0.8348801811653037</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>1.129702167440231e-06</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>0</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>0.0591695580698831</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0.9408304419301168</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2728,13 +5510,13 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.46444672065007</v>
+        <v>0.6365310387984713</v>
       </c>
       <c r="H36" t="n">
-        <v>0.5355401989394237</v>
+        <v>0.3634581633266717</v>
       </c>
       <c r="I36" t="n">
-        <v>1.300635409043409e-05</v>
+        <v>1.072381844118239e-05</v>
       </c>
       <c r="J36" t="n">
         <v>0.3739982832923364</v>
@@ -2755,7 +5537,7 @@
         <v>8.635030369095575e-09</v>
       </c>
       <c r="P36" t="n">
-        <v>1.642290256120999e-06</v>
+        <v>1.642290256121e-06</v>
       </c>
       <c r="Q36" t="n">
         <v>1.247961652715586e-05</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>5.55394373280006e-07</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0.0002025763028935</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0.9997974236971066</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -2792,13 +5652,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9902246140240512</v>
+        <v>0.9913495400031198</v>
       </c>
       <c r="H37" t="n">
-        <v>0.009762164382015551</v>
+        <v>0.008639459739476101</v>
       </c>
       <c r="I37" t="n">
-        <v>1.314753751737573e-05</v>
+        <v>1.092620098841996e-05</v>
       </c>
       <c r="J37" t="n">
         <v>0.8348707794007275</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>8.961447505418687e-06</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>0</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0.4992071931610476</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0.5007928068389523</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1.072730150678061e-06</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0.9999989272698494</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9936740041351801</v>
+        <v>0.9939472177604676</v>
       </c>
       <c r="H38" t="n">
-        <v>0.00631260782355595</v>
+        <v>0.00604151482609275</v>
       </c>
       <c r="I38" t="n">
-        <v>1.331398484800672e-05</v>
+        <v>1.119335702399322e-05</v>
       </c>
       <c r="J38" t="n">
         <v>0.4843644704121026</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.0001344061204875055</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>0</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0.9977359280079312</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0.00226407199206875</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>0.0295916334840086</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0.9704083665159914</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2920,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.9965459891442181</v>
+        <v>0.9966545985648649</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0034401050565569</v>
+        <v>0.003333298218996125</v>
       </c>
       <c r="I39" t="n">
-        <v>1.38317428092687e-05</v>
+        <v>1.202915972325144e-05</v>
       </c>
       <c r="J39" t="n">
         <v>0.1120767544438856</v>
@@ -2947,10 +5963,10 @@
         <v>0.0173154493441119</v>
       </c>
       <c r="P39" t="n">
-        <v>0.5170955474865535</v>
+        <v>0.5170955474865536</v>
       </c>
       <c r="Q39" t="n">
-        <v>7.582874075325477e-06</v>
+        <v>7.582874075325478e-06</v>
       </c>
       <c r="R39" t="n">
         <v>0.0011356469356253</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.00121727512808725</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0.7476149335176204</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0.002385066482379525</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.04437892162055418</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0.7056210783794458</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2984,13 +6078,13 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.998544117774091</v>
+        <v>0.9985912000591458</v>
       </c>
       <c r="H40" t="n">
-        <v>0.00144218188898425</v>
+        <v>0.00139684417432875</v>
       </c>
       <c r="I40" t="n">
-        <v>1.362628050874287e-05</v>
+        <v>1.188171010966781e-05</v>
       </c>
       <c r="J40" t="n">
         <v>0.07679866349453071</v>
@@ -3011,7 +6105,7 @@
         <v>0.03715752757598515</v>
       </c>
       <c r="P40" t="n">
-        <v>0.3459682792757821</v>
+        <v>0.345968279275782</v>
       </c>
       <c r="Q40" t="n">
         <v>9.03388981803645e-06</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.0009425390200531</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0.4981419360714537</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0.0018580639285463</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.0295847926982331</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0.4704152073017669</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_8x8_b1_dat-524288_wt-32768_int8/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_8x8_b1_dat-524288_wt-32768_int8/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,307 +425,312 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.9935126358524562</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.0064774405322694</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>9.849558858795656e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.8348764953403011</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.0128848528575348</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.0341702431564638</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>5.28743588265252e-06</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0807672183146627</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.0279555496584252</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>0.0062150199384119</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>0.0031242595448253</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>1.542975715485955e-07</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>8.45399505050083e-07</v>
       </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -739,38 +744,38 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE2" t="n">
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
         <v>0.0591694709353376</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AJ2" t="n">
         <v>0.9408305290646624</v>
       </c>
-      <c r="AI2" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ2" t="n">
-        <v>0</v>
-      </c>
       <c r="AK2" t="n">
         <v>1</v>
       </c>
@@ -784,10 +789,10 @@
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -796,81 +801,87 @@
         <v>1</v>
       </c>
       <c r="AS2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV2" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9957876585236424</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0042010725225242</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1.119489741759265e-05</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.6533730019874479</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.1867147477092027</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.1378884276974253</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0043432428926929</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>0.0139653480859252</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0017450319553538</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>4.865421376964436e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>0.0017692301884525</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>3.04730017366788e-05</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>9.666661736787623e-05</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>6.88903866022055e-05</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>0</v>
-      </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
@@ -881,38 +892,38 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
         <v>0.0591692535935819</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AJ3" t="n">
         <v>0.9408307464064182</v>
       </c>
-      <c r="AI3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>0</v>
-      </c>
       <c r="AK3" t="n">
         <v>1</v>
       </c>
@@ -926,10 +937,10 @@
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -938,123 +949,129 @@
         <v>1</v>
       </c>
       <c r="AS3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV3" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.998627882358355</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.001360093224445</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>1.195036078419393e-05</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.1270936853959442</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.7113480858124837</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.048088291903377</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0042377050200226</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.0979749516449977</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0095575413156486</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>1.354133705851717e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>1.027409957954611e-05</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0009753978094309</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0005999082284508</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>0.0001127305799429</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC4" t="n">
         <v>0</v>
       </c>
       <c r="AD4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG4" t="n">
         <v>0.9977560986321156</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AH4" t="n">
         <v>0.0022439013678844</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AI4" t="n">
         <v>0.0591698558388248</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AJ4" t="n">
         <v>0.9408301441611751</v>
       </c>
-      <c r="AI4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>0</v>
-      </c>
       <c r="AK4" t="n">
         <v>1</v>
       </c>
@@ -1068,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -1080,123 +1097,129 @@
         <v>1</v>
       </c>
       <c r="AS4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV4" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.997181177076602</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0028069800279304</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>1.176883905189352e-05</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.2397922243700651</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.5970466778696649</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.061085252715503</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.0062249998525152</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0812943909433323</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.0130635711511895</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>8.764989235048805e-07</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>5.646874424495404e-06</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0008553556769254</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0001627249247172</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0004682050663232</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
         <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
         <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG5" t="n">
         <v>0.997693537504767</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AH5" t="n">
         <v>0.002306462495233</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AI5" t="n">
         <v>0.0591741576156335</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AJ5" t="n">
         <v>0.9408258423843664</v>
       </c>
-      <c r="AI5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>0</v>
-      </c>
       <c r="AK5" t="n">
         <v>1</v>
       </c>
@@ -1210,10 +1233,10 @@
         <v>0</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -1222,123 +1245,129 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV5" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9983876091132184</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0016002678487227</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>1.204898164318243e-05</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.1778168759913771</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.6609050142338452</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.0497824335413831</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.0037227594334877</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.0931976925956593</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.0124248480570995</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>6.730780966700538e-07</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>1.792050504037523e-05</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0015778111066602</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>4.148787071712233e-05</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0005124095302176</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="n">
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
         <v>0.997769684316312</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AH6" t="n">
         <v>0.002230315683688</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AI6" t="n">
         <v>0.0591758843019952</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AJ6" t="n">
         <v>0.9408241156980048</v>
       </c>
-      <c r="AI6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ6" t="n">
-        <v>0</v>
-      </c>
       <c r="AK6" t="n">
         <v>1</v>
       </c>
@@ -1352,10 +1381,10 @@
         <v>0</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
         <v>0</v>
@@ -1364,81 +1393,87 @@
         <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV6" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.9938117585028076</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0061770389265429</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1.112851423369073e-05</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.8348770273212863</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.009768545127040401</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.0285300653416497</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>5.334646330170371e-06</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.08875822219667689</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0095086898104846</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>3.608140739794815e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>0.0253771563705644</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>6.94138306616822e-08</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>5.765175740508796e-07</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>0.003170631057407</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>0</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
@@ -1449,19 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
         <v>0</v>
@@ -1470,17 +1505,17 @@
         <v>1</v>
       </c>
       <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI7" t="n">
         <v>0.059169649138453</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AJ7" t="n">
         <v>0.9408303508615468</v>
       </c>
-      <c r="AI7" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>0</v>
-      </c>
       <c r="AK7" t="n">
         <v>1</v>
       </c>
@@ -1494,10 +1529,10 @@
         <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
         <v>0</v>
@@ -1506,104 +1541,110 @@
         <v>1</v>
       </c>
       <c r="AS7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.9966561710628696</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0033326563843456</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>1.109849636893409e-05</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.8040376336929038</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.0365691283605194</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0859502018010825</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0040199876389851</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.052780079083574</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.0090471521728063</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>4.6607765657427e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>0.0060478754362996</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>9.829428136086295e-07</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>3.31037674990938e-05</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0015091202705345</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
         <v>0</v>
       </c>
       <c r="AD8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
         <v>0</v>
@@ -1612,17 +1653,17 @@
         <v>1</v>
       </c>
       <c r="AG8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI8" t="n">
         <v>0.0591694170261715</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AJ8" t="n">
         <v>0.9408305829738286</v>
       </c>
-      <c r="AI8" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>0</v>
-      </c>
       <c r="AK8" t="n">
         <v>1</v>
       </c>
@@ -1636,10 +1677,10 @@
         <v>0</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
         <v>0</v>
@@ -1648,81 +1689,87 @@
         <v>1</v>
       </c>
       <c r="AS8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV8" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9974299600561068</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0025562538250257</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>1.371206245168927e-05</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.8251655714516919</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.0175372451766649</v>
       </c>
-      <c r="L9" t="n">
+      <c r="N9" t="n">
         <v>7.874967226758982e-09</v>
       </c>
-      <c r="M9" t="n">
+      <c r="O9" t="n">
         <v>0.0019491141562022</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>7.842680834335289e-06</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>6.150158396316899e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.155330801069048</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>6.354499609557969e-07</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>2.45555124452297e-06</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>1.023745739478731e-07</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
@@ -1733,37 +1780,37 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA9" t="n">
         <v>0</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
         <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG9" t="n">
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK9" t="n">
         <v>1</v>
@@ -1778,10 +1825,10 @@
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
@@ -1790,75 +1837,81 @@
         <v>1</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV9" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.9995232528800918</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0004641697450873</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>1.250331840518282e-05</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0544590400976317</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.7880475875508054</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.0011987194301098</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>1.079349299162575e-05</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>1.7426652050163e-07</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.1553228337123175</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0009607773932075</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
@@ -1875,13 +1928,13 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC10" t="n">
         <v>0</v>
@@ -1902,28 +1955,28 @@
         <v>0</v>
       </c>
       <c r="AI10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ10" t="n">
         <v>0</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL10" t="n">
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ10" t="n">
         <v>0</v>
@@ -1932,75 +1985,81 @@
         <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.9998541419167586</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>0.0001331275496864</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>1.265647713927788e-05</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>0.0002731173916353</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.9677395317167856</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.0005893377813455</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>1.087785185071484e-05</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>7.408816877152395e-09</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>0.0310882875797958</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>0.0002987662133543</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
@@ -2017,13 +2076,13 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC11" t="n">
         <v>0</v>
@@ -2044,28 +2103,28 @@
         <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
         <v>0</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL11" t="n">
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ11" t="n">
         <v>0</v>
@@ -2074,81 +2133,87 @@
         <v>1</v>
       </c>
       <c r="AS11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.9984813890240608</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0015051246672201</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>1.341225230335372e-05</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>0.545961535341396</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
         <v>7.924890944439248e-09</v>
       </c>
-      <c r="M12" t="n">
+      <c r="O12" t="n">
         <v>0.0040917606973372</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>4.970715545886123e-06</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>8.621111920645587e-10</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.2889755567033945</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.1553299528009764</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>0.0001425442341398</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0054930977568422</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>4.989069498768733e-07</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>0</v>
-      </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
@@ -2159,25 +2224,25 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC12" t="n">
         <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG12" t="n">
         <v>0</v>
@@ -2186,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2204,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
@@ -2216,81 +2281,87 @@
         <v>1</v>
       </c>
       <c r="AS12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV12" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.9995771474077644</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>0.0004095366623882</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>1.324187343157978e-05</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.4585621839624038</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
-        <v>0</v>
-      </c>
       <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
         <v>1.736875909108222e-06</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>7.19340217603813e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.4170197503346373</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>0.1165009200550751</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>2.234785144520891e-06</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>0.0079058983514179</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>8.176820366136963e-09</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
@@ -2301,25 +2372,25 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG13" t="n">
         <v>0</v>
@@ -2328,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2346,10 +2417,10 @@
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
@@ -2358,81 +2429,87 @@
         <v>1</v>
       </c>
       <c r="AS13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9979201499628388</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0020663091380945</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>1.346684265080122e-05</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.6268229243187448</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
         <v>8.214432235346224e-09</v>
       </c>
-      <c r="M14" t="n">
+      <c r="O14" t="n">
         <v>0.0057974579385447</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>4.741398601492761e-06</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>1.829682908787304e-10</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.2081142181736767</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.1553299301902241</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>1.804210136296128e-06</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.0037321187095409</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>0.0001967226067144</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
@@ -2443,34 +2520,34 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC14" t="n">
         <v>0</v>
       </c>
       <c r="AD14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -2488,10 +2565,10 @@
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
@@ -2500,78 +2577,84 @@
         <v>1</v>
       </c>
       <c r="AS14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.9994306098579584</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>0.0005560870569037</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>1.322902872211719e-05</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>0.682547168259441</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>9.681630117391977e-07</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>6.401587345653962e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.179765252717811</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.1294451189674189</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>2.143978162512778e-06</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.008232872270393401</v>
       </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
       <c r="V15" t="n">
         <v>0</v>
       </c>
@@ -2585,25 +2668,25 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA15" t="n">
         <v>0</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
       </c>
       <c r="AD15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG15" t="n">
         <v>0</v>
@@ -2612,7 +2695,7 @@
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -2630,10 +2713,10 @@
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
@@ -2642,81 +2725,87 @@
         <v>1</v>
       </c>
       <c r="AS15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.9997226840382528</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>0.0002647115581634</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>1.253034716798421e-05</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>0.1748085214302703</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>0.0012174359399308</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>4.213963585288172e-08</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>5.550676271313766e-06</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>1.132254705919821e-05</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.7118877780724164</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.1035581628852104</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>3.774629197121858e-06</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0085073060188657</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>3.160472688966129e-08</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>0</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
@@ -2727,25 +2816,25 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC16" t="n">
         <v>0</v>
       </c>
       <c r="AD16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG16" t="n">
         <v>0</v>
@@ -2754,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -2772,10 +2861,10 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
@@ -2784,81 +2873,87 @@
         <v>1</v>
       </c>
       <c r="AS16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV16" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.9990654127194044</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0009214914810683</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>1.302174311162207e-05</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.2101986987663695</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0008295438925082</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>7.538926401390794e-05</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.005353258833199</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>9.756447494533727e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>3.706277288068445e-09</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.6287073463827871</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.1518070187248878</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>0.0005308149295432</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0018838493612558</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0006042456352474</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0</v>
-      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
@@ -2869,25 +2964,25 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
         <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC17" t="n">
         <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG17" t="n">
         <v>1</v>
@@ -2914,10 +3009,10 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
         <v>0</v>
@@ -2926,81 +3021,87 @@
         <v>1</v>
       </c>
       <c r="AS17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9997378424585046</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>0.00024927215548</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>1.281132959945893e-05</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>0.3242934006503286</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>4.109083627006373e-06</v>
       </c>
-      <c r="L18" t="n">
+      <c r="N18" t="n">
         <v>3.313497873057887e-08</v>
       </c>
-      <c r="M18" t="n">
+      <c r="O18" t="n">
         <v>5.794492242351173e-06</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>1.286064870043477e-05</v>
       </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
         <v>0.5759166552777213</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>0.090612780897841</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>3.746086980295121e-06</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.0091504904462</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>5.522496455097102e-08</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
@@ -3011,25 +3112,25 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
         <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" t="n">
         <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
         <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG18" t="n">
         <v>0</v>
@@ -3038,7 +3139,7 @@
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
@@ -3056,10 +3157,10 @@
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
@@ -3068,75 +3169,81 @@
         <v>1</v>
       </c>
       <c r="AS18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV18" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.9996490877540858</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0003381793562304</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>1.265883326800121e-05</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>0.0540303549031347</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.8372260806889252</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.0005661298939684</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>1.080758916779583e-05</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>2.186961568671076e-08</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.1075412667362564</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0006252642625157</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
@@ -3153,13 +3260,13 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC19" t="n">
         <v>0</v>
@@ -3180,28 +3287,28 @@
         <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
         <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL19" t="n">
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
         <v>0</v>
@@ -3210,75 +3317,81 @@
         <v>1</v>
       </c>
       <c r="AS19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV19" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9997956779211638</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>0.0001915326010309</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>1.271542138952982e-05</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.1577470771767243</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.7950724467015039</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>0.0004172513075412</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>7.278220925970922e-06</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>9.736049144059359e-09</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0466127650185822</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.0001430977822574</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
@@ -3295,13 +3408,13 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
         <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC20" t="n">
         <v>0</v>
@@ -3322,28 +3435,28 @@
         <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
         <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL20" t="n">
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
         <v>0</v>
@@ -3352,75 +3465,81 @@
         <v>1</v>
       </c>
       <c r="AS20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV20" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9992892497710084</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0006976641539212</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>1.30120186546188e-05</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.1141116026430236</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.7413567616256698</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.00129000804246</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>1.041805291218198e-05</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>2.083891634969577e-07</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.1418219503135353</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0014089768768198</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
@@ -3437,13 +3556,13 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA21" t="n">
         <v>0</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC21" t="n">
         <v>0</v>
@@ -3464,28 +3583,28 @@
         <v>0</v>
       </c>
       <c r="AI21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ21" t="n">
         <v>0</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL21" t="n">
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ21" t="n">
         <v>0</v>
@@ -3494,72 +3613,78 @@
         <v>1</v>
       </c>
       <c r="AS21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV21" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.6100778852204668</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3899088624841677</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>1.317823894983643e-05</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0010598566252329</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9931896769916282</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>2.197029589491661e-07</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>4.071739273694216e-07</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>2.279564064555377e-08</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.005749742654196</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
-        <v>0</v>
-      </c>
       <c r="T22" t="n">
         <v>0</v>
       </c>
@@ -3579,25 +3704,25 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA22" t="n">
         <v>0</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC22" t="n">
         <v>0</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE22" t="n">
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -3606,28 +3731,28 @@
         <v>0</v>
       </c>
       <c r="AI22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ22" t="n">
         <v>0</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL22" t="n">
         <v>0</v>
       </c>
       <c r="AM22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN22" t="n">
         <v>0</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ22" t="n">
         <v>0</v>
@@ -3639,78 +3764,84 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.849619843055416</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.1503665030342704</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>1.357985389770894e-05</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>0.7490931311545371</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.2482373414520885</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>1.89039205494835e-05</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>4.787352685734052e-06</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>3.296296503530885e-06</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0026405754794474</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>7.535655541265991e-07</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>9.859704452695458e-07</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>1.50751772998031e-07</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
@@ -3721,37 +3852,37 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC23" t="n">
         <v>0</v>
       </c>
       <c r="AD23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE23" t="n">
         <v>0</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG23" t="n">
         <v>0</v>
       </c>
       <c r="AH23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK23" t="n">
         <v>1</v>
@@ -3766,10 +3897,10 @@
         <v>0</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
@@ -3778,81 +3909,87 @@
         <v>1</v>
       </c>
       <c r="AS23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV23" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9969203171364168</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0030660794901345</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>1.352931703307087e-05</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.7319165460057344</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
         <v>3.317161463648107e-08</v>
       </c>
-      <c r="M24" t="n">
+      <c r="O24" t="n">
         <v>0.0073963639639113</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>4.385975833155048e-06</v>
       </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
-      <c r="P24" t="n">
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
         <v>0.1030307140283908</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.1553196338975889</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>1.701916952541651e-06</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0023301645716391</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>3.824119192613262e-07</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>0</v>
-      </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
@@ -3863,25 +4000,25 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC24" t="n">
         <v>0</v>
       </c>
       <c r="AD24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE24" t="n">
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG24" t="n">
         <v>0</v>
@@ -3890,7 +4027,7 @@
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
@@ -3908,10 +4045,10 @@
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
@@ -3920,81 +4057,87 @@
         <v>1</v>
       </c>
       <c r="AS24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV24" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.99822173033103</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0017650888944236</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>1.310671813053641e-05</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.1886735821305832</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0009551496245314</v>
       </c>
-      <c r="L25" t="n">
+      <c r="N25" t="n">
         <v>8.631474785572771e-08</v>
       </c>
-      <c r="M25" t="n">
+      <c r="O25" t="n">
         <v>0.0069819413429327</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>7.020901908016187e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>7.877086709778806e-09</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.6465422709490132</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.1553167306232449</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0006158506245095</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.0003917015894982</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0005155839655283</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>0</v>
-      </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
@@ -4005,25 +4148,25 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA25" t="n">
         <v>0</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC25" t="n">
         <v>0</v>
       </c>
       <c r="AD25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG25" t="n">
         <v>1</v>
@@ -4050,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
         <v>0</v>
@@ -4062,123 +4205,129 @@
         <v>1</v>
       </c>
       <c r="AS25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV25" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.9986642406912952</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0013236604156025</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>1.202483668635819e-05</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.054155158835871</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.000848524687605</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.0382858697017639</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.003983525150984</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0910518887906408</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0267776151395616</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.7824741558372607</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>5.488971115664638e-06</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>0.0005399506622531</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0002569913889748</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0016207567775533</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA26" t="n">
         <v>0</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC26" t="n">
         <v>0</v>
       </c>
       <c r="AD26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG26" t="n">
         <v>0.9977146818047896</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AH26" t="n">
         <v>0.0022853181952102</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AI26" t="n">
         <v>0.0591701533909508</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AJ26" t="n">
         <v>0.9408298466090492</v>
       </c>
-      <c r="AI26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
       <c r="AK26" t="n">
         <v>1</v>
       </c>
@@ -4192,10 +4341,10 @@
         <v>0</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
         <v>0</v>
@@ -4204,123 +4353,129 @@
         <v>1</v>
       </c>
       <c r="AS26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV26" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.9954259104361576</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.004562655570326</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>1.135993710049844e-05</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.7882756533315015</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.0524010163783766</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.1080435183069254</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.0039335998119396</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.0337678154696597</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0106112866643418</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>4.118541104329545e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.0029123506370686</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>1.615109825870262e-05</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>2.411262824865157e-06</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>3.200444158288361e-05</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
       </c>
       <c r="AD27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="n">
         <v>0.9984650367362796</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AH27" t="n">
         <v>0.0015349632637204</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AI27" t="n">
         <v>0.0591694422784894</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AJ27" t="n">
         <v>0.9408305577215106</v>
       </c>
-      <c r="AI27" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
       <c r="AK27" t="n">
         <v>1</v>
       </c>
@@ -4334,10 +4489,10 @@
         <v>0</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
         <v>0</v>
@@ -4346,122 +4501,128 @@
         <v>1</v>
       </c>
       <c r="AS27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.9982289232609139</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0017594505921931</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>1.155209047714058e-05</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.3628753196206373</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.0961450322080285</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.006211974983079</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.0425338804042215</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.016640519078381</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.4723445499442209</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>9.283059906026031e-06</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>4.414732866450059e-05</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.0029745035709341</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.000220715745511</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA28" t="n">
         <v>0</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC28" t="n">
         <v>0</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG28" t="n">
         <v>0.9977795906018876</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AH28" t="n">
         <v>0.0022204093981123</v>
       </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>1</v>
-      </c>
       <c r="AI28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK28" t="n">
         <v>1</v>
@@ -4476,10 +4637,10 @@
         <v>0</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
         <v>0</v>
@@ -4488,123 +4649,129 @@
         <v>1</v>
       </c>
       <c r="AS28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9955043119590306</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.0044841352278984</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>1.147875665545848e-05</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.456245978587135</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.0794593203957806</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0073987599262539</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0517774098471159</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0232074834731449</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.3791755542656134</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>7.269696105626184e-06</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0012769352910598</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0007717618461598</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.0006794430305623</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y29" t="n">
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA29" t="n">
         <v>0</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC29" t="n">
         <v>0</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG29" t="n">
         <v>0.9977687856899746</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AH29" t="n">
         <v>0.0022312143100253</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AI29" t="n">
         <v>0.0591808907862606</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AJ29" t="n">
         <v>0.9408191092137392</v>
       </c>
-      <c r="AI29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ29" t="n">
-        <v>0</v>
-      </c>
       <c r="AK29" t="n">
         <v>1</v>
       </c>
@@ -4618,10 +4785,10 @@
         <v>0</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -4630,72 +4797,78 @@
         <v>1</v>
       </c>
       <c r="AS29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV29" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.6100708955441373</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.3899167062750741</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>1.232412437279761e-05</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0015971629698457</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.9938980931706958</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
-        <v>0</v>
-      </c>
       <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>4.118011218114322e-08</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>3.648232445414914e-08</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.004504592140606</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -4715,25 +4888,25 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
         <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
       </c>
       <c r="AD30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE30" t="n">
         <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -4742,13 +4915,13 @@
         <v>0</v>
       </c>
       <c r="AI30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ30" t="n">
         <v>0</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL30" t="n">
         <v>0</v>
@@ -4763,7 +4936,7 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
@@ -4775,78 +4948,84 @@
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.9954182950692519</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.0045685472938587</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>1.308358047353169e-05</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>0.2343492812055353</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.0639445824504024</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.0044275476887313</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>1.211662860388774e-05</v>
       </c>
-      <c r="O31" t="n">
+      <c r="Q31" t="n">
         <v>0.6058544733164</v>
       </c>
-      <c r="P31" t="n">
+      <c r="R31" t="n">
         <v>3.923607533021611e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.091405780757702</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>1.003461258760855e-06</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>3.059004401809508e-07</v>
       </c>
-      <c r="T31" t="n">
+      <c r="V31" t="n">
         <v>9.109269773091807e-07</v>
       </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
-      <c r="V31" t="n">
-        <v>0</v>
-      </c>
       <c r="W31" t="n">
         <v>0</v>
       </c>
@@ -4857,37 +5036,37 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA31" t="n">
         <v>0</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC31" t="n">
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE31" t="n">
         <v>0</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG31" t="n">
         <v>0</v>
       </c>
       <c r="AH31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK31" t="n">
         <v>1</v>
@@ -4902,10 +5081,10 @@
         <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
@@ -4914,78 +5093,84 @@
         <v>1</v>
       </c>
       <c r="AS31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV31" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.6136184078730865</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.3863680658256649</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>1.345224483284425e-05</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>0.0005839822143495</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.9987271041001896</v>
       </c>
-      <c r="L32" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" t="n">
+      <c r="N32" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" t="n">
         <v>5.903272401875804e-07</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>8.167439432550782e-08</v>
       </c>
-      <c r="O32" t="n">
+      <c r="Q32" t="n">
         <v>1.983214322414925e-08</v>
       </c>
-      <c r="P32" t="n">
+      <c r="R32" t="n">
         <v>3.37958185850951e-08</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.0006879831018259</v>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="n">
+      <c r="T32" t="n">
+        <v>0</v>
+      </c>
+      <c r="U32" t="n">
         <v>1.308976227828103e-07</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
         <v>0</v>
       </c>
@@ -4999,25 +5184,25 @@
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA32" t="n">
         <v>0</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC32" t="n">
         <v>0</v>
       </c>
       <c r="AD32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE32" t="n">
         <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -5032,7 +5217,7 @@
         <v>0</v>
       </c>
       <c r="AK32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL32" t="n">
         <v>0</v>
@@ -5044,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
@@ -5059,72 +5244,78 @@
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.4000551901277922</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.5999340180037078</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>1.071781208420934e-05</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>0.0011647845300437</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.9982856955606684</v>
       </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
         <v>3.258164124285801e-05</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.0001721581691947</v>
       </c>
-      <c r="O33" t="n">
+      <c r="Q33" t="n">
         <v>0.0003440484047562</v>
       </c>
-      <c r="P33" t="n">
+      <c r="R33" t="n">
         <v>7.561544785276933e-08</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>5.163671725390783e-07</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>6.565505764578927e-08</v>
       </c>
-      <c r="S33" t="n">
-        <v>0</v>
-      </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
       <c r="U33" t="n">
         <v>0</v>
       </c>
@@ -5141,37 +5332,37 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA33" t="n">
         <v>0</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC33" t="n">
         <v>0</v>
       </c>
       <c r="AD33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE33" t="n">
         <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
       </c>
       <c r="AH33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI33" t="n">
         <v>0</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK33" t="n">
         <v>0</v>
@@ -5180,16 +5371,16 @@
         <v>0</v>
       </c>
       <c r="AM33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN33" t="n">
         <v>0</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
         <v>0</v>
@@ -5201,107 +5392,113 @@
         <v>0</v>
       </c>
       <c r="AT33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.458233490801388</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.5417562358642501</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>1.019927794611022e-05</v>
       </c>
-      <c r="J34" t="n">
+      <c r="L34" t="n">
         <v>0.0006782071499024</v>
       </c>
-      <c r="K34" t="n">
+      <c r="M34" t="n">
         <v>0.9987330198233204</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>3.561075221017024e-05</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.0003675064476678</v>
       </c>
-      <c r="O34" t="n">
+      <c r="Q34" t="n">
         <v>0.0001836445047424</v>
       </c>
-      <c r="P34" t="n">
+      <c r="R34" t="n">
         <v>1.540462685903923e-07</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>1.187808070376075e-06</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>2.150353722894214e-07</v>
       </c>
-      <c r="S34" t="n">
+      <c r="U34" t="n">
         <v>1.433569148596122e-07</v>
       </c>
-      <c r="T34" t="n">
+      <c r="V34" t="n">
         <v>2.362977859917696e-07</v>
       </c>
-      <c r="U34" t="n">
-        <v>0</v>
-      </c>
-      <c r="V34" t="n">
-        <v>1</v>
-      </c>
       <c r="W34" t="n">
         <v>0</v>
       </c>
       <c r="X34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y34" t="n">
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA34" t="n">
         <v>0</v>
       </c>
       <c r="AB34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC34" t="n">
         <v>0</v>
       </c>
       <c r="AD34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE34" t="n">
         <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -5310,28 +5507,28 @@
         <v>0</v>
       </c>
       <c r="AI34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ34" t="n">
         <v>0</v>
       </c>
       <c r="AK34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AL34" t="n">
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
@@ -5340,81 +5537,87 @@
         <v>1</v>
       </c>
       <c r="AS34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV34" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.991653459109336</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.008335592112708149</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>1.087472153986128e-05</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.8348801811653037</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.0097692242414333</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.03663513747218995</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>5.461701623820511e-06</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.08193873118950035</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.0069811727951022</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>3.372046018529941e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.02978481039583845</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>1.135042379881929e-07</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>5.917301682749477e-07</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>1.129702167440231e-06</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
@@ -5425,19 +5628,19 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA35" t="n">
         <v>0</v>
       </c>
       <c r="AB35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC35" t="n">
         <v>0</v>
       </c>
       <c r="AD35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE35" t="n">
         <v>0</v>
@@ -5446,17 +5649,17 @@
         <v>1</v>
       </c>
       <c r="AG35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI35" t="n">
         <v>0.0591695580698831</v>
       </c>
-      <c r="AH35" t="n">
+      <c r="AJ35" t="n">
         <v>0.9408304419301168</v>
       </c>
-      <c r="AI35" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
       <c r="AK35" t="n">
         <v>1</v>
       </c>
@@ -5470,10 +5673,10 @@
         <v>0</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
         <v>0</v>
@@ -5482,81 +5685,87 @@
         <v>1</v>
       </c>
       <c r="AS35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV35" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.6365310387984713</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.3634581633266717</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>1.072381844118239e-05</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.3739982832923364</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.6245097931475432</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.00119836763043615</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>1.929353157117453e-05</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.0002590682912973</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>8.635030369095575e-09</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>1.642290256121e-06</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>1.247961652715586e-05</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>2.154582437746516e-07</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>2.186559692822662e-07</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>5.55394373280006e-07</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>0</v>
-      </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
@@ -5567,55 +5776,55 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA36" t="n">
         <v>0</v>
       </c>
       <c r="AB36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC36" t="n">
         <v>0</v>
       </c>
       <c r="AD36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE36" t="n">
         <v>0</v>
       </c>
       <c r="AF36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AG36" t="n">
+      <c r="AI36" t="n">
         <v>0.0002025763028935</v>
       </c>
-      <c r="AH36" t="n">
+      <c r="AJ36" t="n">
         <v>0.9997974236971066</v>
       </c>
-      <c r="AI36" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>0</v>
-      </c>
       <c r="AK36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AL36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM36" t="n">
-        <v>1</v>
-      </c>
       <c r="AN36" t="n">
         <v>0</v>
       </c>
       <c r="AO36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
         <v>0</v>
@@ -5624,81 +5833,87 @@
         <v>1</v>
       </c>
       <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AT36" t="n">
+      <c r="AV36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9913495400031198</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.008639459739476101</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>1.092620098841996e-05</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.8348707794007275</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.0014221964531693</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.1049789137650486</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.0083638515135882</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.04374885023774875</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.00377858432646575</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>4.331014006527061e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.0028214946771181</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>1.009369622013334e-06</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>9.537385838540533e-07</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>8.961447505418687e-06</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>0</v>
-      </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
@@ -5709,38 +5924,38 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
       </c>
       <c r="AB37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC37" t="n">
         <v>0</v>
       </c>
       <c r="AD37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="n">
         <v>0.4992071931610476</v>
       </c>
-      <c r="AF37" t="n">
+      <c r="AH37" t="n">
         <v>0.5007928068389523</v>
       </c>
-      <c r="AG37" t="n">
+      <c r="AI37" t="n">
         <v>1.072730150678061e-06</v>
       </c>
-      <c r="AH37" t="n">
+      <c r="AJ37" t="n">
         <v>0.9999989272698494</v>
       </c>
-      <c r="AI37" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ37" t="n">
-        <v>0</v>
-      </c>
       <c r="AK37" t="n">
         <v>1</v>
       </c>
@@ -5754,10 +5969,10 @@
         <v>0</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
         <v>0</v>
@@ -5766,81 +5981,87 @@
         <v>1</v>
       </c>
       <c r="AS37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV37" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9939472177604676</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.00604151482609275</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>1.119335702399322e-05</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.4843644704121026</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.09421115639087915</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.00844207574992945</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.05743671777437765</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.003240005001722</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.3506282246402888</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.000438621595200904</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>4.658341167251918e-05</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.00105766484692325</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.0001344061204875055</v>
       </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>0</v>
-      </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
@@ -5851,38 +6072,38 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA38" t="n">
         <v>0</v>
       </c>
       <c r="AB38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC38" t="n">
         <v>0</v>
       </c>
       <c r="AD38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG38" t="n">
         <v>0.9977359280079312</v>
       </c>
-      <c r="AF38" t="n">
+      <c r="AH38" t="n">
         <v>0.00226407199206875</v>
       </c>
-      <c r="AG38" t="n">
+      <c r="AI38" t="n">
         <v>0.0295916334840086</v>
       </c>
-      <c r="AH38" t="n">
+      <c r="AJ38" t="n">
         <v>0.9704083665159914</v>
       </c>
-      <c r="AI38" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>0</v>
-      </c>
       <c r="AK38" t="n">
         <v>1</v>
       </c>
@@ -5896,10 +6117,10 @@
         <v>0</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
@@ -5908,140 +6129,146 @@
         <v>1</v>
       </c>
       <c r="AS38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV38" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9966545985648649</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.003333298218996125</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>1.202915972325144e-05</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.1120767544438856</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2356191592312236</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.02675253283550455</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.0038229040379737</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.0848919865594461</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.0173154493441119</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.5170955474865536</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>7.582874075325478e-06</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.0011356469356253</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>6.508706709689333e-05</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.00121727512808725</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
         <v>0.5</v>
       </c>
-      <c r="W39" t="n">
-        <v>0</v>
-      </c>
-      <c r="X39" t="n">
-        <v>0</v>
-      </c>
       <c r="Y39" t="n">
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA39" t="n">
         <v>0</v>
       </c>
       <c r="AB39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC39" t="n">
         <v>0</v>
       </c>
       <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AE39" t="n">
+      <c r="AG39" t="n">
         <v>0.7476149335176204</v>
       </c>
-      <c r="AF39" t="n">
+      <c r="AH39" t="n">
         <v>0.002385066482379525</v>
       </c>
-      <c r="AG39" t="n">
+      <c r="AI39" t="n">
         <v>0.04437892162055418</v>
       </c>
-      <c r="AH39" t="n">
+      <c r="AJ39" t="n">
         <v>0.7056210783794458</v>
       </c>
-      <c r="AI39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ39" t="n">
-        <v>0</v>
-      </c>
       <c r="AK39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AL39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM39" t="n">
-        <v>1</v>
-      </c>
       <c r="AN39" t="n">
         <v>0</v>
       </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ39" t="n">
         <v>0</v>
@@ -6050,140 +6277,146 @@
         <v>1</v>
       </c>
       <c r="AS39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV39" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.9985912000591458</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.00139684417432875</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>1.188171010966781e-05</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.07679866349453071</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.4392573090686404</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.0114195898516671</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.0019524096471215</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.0853204914664857</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.03715752757598515</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.345968279275782</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>9.03388981803645e-06</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.0011455577732388</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>2.852488026144282e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.0009425390200531</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
       <c r="X40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y40" t="n">
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA40" t="n">
         <v>0</v>
       </c>
       <c r="AB40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC40" t="n">
         <v>0</v>
       </c>
       <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AE40" t="n">
+      <c r="AG40" t="n">
         <v>0.4981419360714537</v>
       </c>
-      <c r="AF40" t="n">
+      <c r="AH40" t="n">
         <v>0.0018580639285463</v>
       </c>
-      <c r="AG40" t="n">
+      <c r="AI40" t="n">
         <v>0.0295847926982331</v>
       </c>
-      <c r="AH40" t="n">
+      <c r="AJ40" t="n">
         <v>0.4704152073017669</v>
       </c>
-      <c r="AI40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ40" t="n">
-        <v>0</v>
-      </c>
       <c r="AK40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AL40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM40" t="n">
-        <v>1</v>
-      </c>
       <c r="AN40" t="n">
         <v>0</v>
       </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ40" t="n">
         <v>0</v>
@@ -6192,9 +6425,15 @@
         <v>1</v>
       </c>
       <c r="AS40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV40" t="n">
         <v>0</v>
       </c>
     </row>
